--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/2528-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/2528-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C6ED9985-841E-4243-86AA-96A98AA3D640}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{835C5200-D97B-4726-9FAB-2C99D9681977}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{0D4C41E6-F236-438C-8473-98917FA3682C}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{D1B29922-D971-4E97-9B82-9DDD807F511E}"/>
   </bookViews>
   <sheets>
     <sheet name="2528-dividend-20260225_0_4" sheetId="2" r:id="rId1"/>
@@ -1517,25 +1517,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1364807-4CCC-401A-A529-620CC69E329F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21862672-2072-4F3E-AE63-2268C0D3E3A0}">
   <dimension ref="A1:R56"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.77734375" customWidth="1"/>
-    <col min="2" max="2" width="11.44140625" customWidth="1"/>
-    <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="4" width="7.77734375" customWidth="1"/>
-    <col min="5" max="5" width="7.44140625" customWidth="1"/>
-    <col min="6" max="6" width="7.77734375" customWidth="1"/>
-    <col min="7" max="9" width="7.44140625" customWidth="1"/>
-    <col min="10" max="10" width="7.77734375" customWidth="1"/>
-    <col min="11" max="13" width="7.44140625" customWidth="1"/>
-    <col min="14" max="14" width="7.77734375" customWidth="1"/>
-    <col min="15" max="17" width="7.44140625" customWidth="1"/>
-    <col min="18" max="18" width="8.109375" customWidth="1"/>
+    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="2" max="2" width="14.25" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="4" max="4" width="9.75" customWidth="1"/>
+    <col min="5" max="5" width="9.375" customWidth="1"/>
+    <col min="6" max="6" width="9.75" customWidth="1"/>
+    <col min="7" max="9" width="9.375" customWidth="1"/>
+    <col min="10" max="10" width="9.75" customWidth="1"/>
+    <col min="11" max="13" width="9.375" customWidth="1"/>
+    <col min="14" max="14" width="9.75" customWidth="1"/>
+    <col min="15" max="17" width="9.375" customWidth="1"/>
+    <col min="18" max="18" width="10.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
@@ -1563,7 +1563,7 @@
       <c r="Q1" s="32"/>
       <c r="R1" s="24"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
@@ -1593,7 +1593,7 @@
       <c r="Q2" s="34"/>
       <c r="R2" s="35"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="25" t="s">
         <v>2</v>
       </c>
@@ -1639,7 +1639,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="27"/>
       <c r="B4" s="28"/>
       <c r="C4" s="7"/>
@@ -1689,7 +1689,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="39">
         <v>2026</v>
       </c>
@@ -1743,7 +1743,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>26</v>
       </c>
@@ -1799,7 +1799,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="41">
         <v>2025</v>
       </c>
@@ -1853,7 +1853,7 @@
         <v>6.16</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="17" t="s">
         <v>26</v>
       </c>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="43" t="s">
         <v>26</v>
       </c>
@@ -1965,7 +1965,7 @@
         <v>6.16</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="44"/>
       <c r="B10" s="22" t="s">
         <v>29</v>
@@ -1987,7 +1987,7 @@
       <c r="Q10" s="48"/>
       <c r="R10" s="48"/>
     </row>
-    <row r="11" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="17" t="s">
         <v>26</v>
       </c>
@@ -2043,7 +2043,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="39">
         <v>2024</v>
       </c>
@@ -2097,7 +2097,7 @@
         <v>1.06</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>26</v>
       </c>
@@ -2153,7 +2153,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
         <v>26</v>
       </c>
@@ -2209,7 +2209,7 @@
         <v>1.06</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="41">
         <v>2023</v>
       </c>
@@ -2263,7 +2263,7 @@
         <v>2.0099999999999998</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="17" t="s">
         <v>26</v>
       </c>
@@ -2319,7 +2319,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="17" t="s">
         <v>26</v>
       </c>
@@ -2375,7 +2375,7 @@
         <v>2.0099999999999998</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="39">
         <v>2022</v>
       </c>
@@ -2429,7 +2429,7 @@
         <v>2.33</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>26</v>
       </c>
@@ -2485,7 +2485,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
         <v>26</v>
       </c>
@@ -2541,7 +2541,7 @@
         <v>2.33</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="41">
         <v>2021</v>
       </c>
@@ -2595,7 +2595,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="17" t="s">
         <v>26</v>
       </c>
@@ -2651,7 +2651,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="17" t="s">
         <v>26</v>
       </c>
@@ -2707,7 +2707,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="39">
         <v>2020</v>
       </c>
@@ -2761,7 +2761,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
         <v>26</v>
       </c>
@@ -2817,7 +2817,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
         <v>26</v>
       </c>
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="41">
         <v>2019</v>
       </c>
@@ -2927,7 +2927,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="17" t="s">
         <v>26</v>
       </c>
@@ -2983,7 +2983,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="17" t="s">
         <v>26</v>
       </c>
@@ -3039,7 +3039,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="39">
         <v>2018</v>
       </c>
@@ -3093,7 +3093,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="41">
         <v>2017</v>
       </c>
@@ -3147,7 +3147,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="39">
         <v>2016</v>
       </c>
@@ -3201,7 +3201,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="41">
         <v>2015</v>
       </c>
@@ -3255,7 +3255,7 @@
         <v>2.06</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="39">
         <v>2014</v>
       </c>
@@ -3309,7 +3309,7 @@
         <v>2.36</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="41">
         <v>2013</v>
       </c>
@@ -3363,7 +3363,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="39">
         <v>2012</v>
       </c>
@@ -3417,7 +3417,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="41">
         <v>2011</v>
       </c>
@@ -3471,7 +3471,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="39">
         <v>2010</v>
       </c>
@@ -3525,7 +3525,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="41">
         <v>2009</v>
       </c>
@@ -3579,7 +3579,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="39">
         <v>2008</v>
       </c>
@@ -3633,7 +3633,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="41">
         <v>2007</v>
       </c>
@@ -3687,7 +3687,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="39">
         <v>2006</v>
       </c>
@@ -3741,7 +3741,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="41">
         <v>2005</v>
       </c>
@@ -3795,7 +3795,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="39">
         <v>2004</v>
       </c>
@@ -3849,7 +3849,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="41">
         <v>2003</v>
       </c>
@@ -3903,7 +3903,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A46" s="39">
         <v>2002</v>
       </c>
@@ -3957,7 +3957,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A47" s="41">
         <v>2001</v>
       </c>
@@ -4011,7 +4011,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A48" s="39">
         <v>2000</v>
       </c>
@@ -4065,7 +4065,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A49" s="41">
         <v>1999</v>
       </c>
@@ -4119,7 +4119,7 @@
         <v>10.4</v>
       </c>
     </row>
-    <row r="50" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A50" s="39">
         <v>1998</v>
       </c>
@@ -4173,7 +4173,7 @@
         <v>5.54</v>
       </c>
     </row>
-    <row r="51" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A51" s="41">
         <v>1997</v>
       </c>
@@ -4227,7 +4227,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="52" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A52" s="39">
         <v>1996</v>
       </c>
@@ -4281,7 +4281,7 @@
         <v>7.04</v>
       </c>
     </row>
-    <row r="53" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A53" s="41">
         <v>1995</v>
       </c>
@@ -4335,7 +4335,7 @@
         <v>4.58</v>
       </c>
     </row>
-    <row r="54" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A54" s="39">
         <v>1994</v>
       </c>
@@ -4389,7 +4389,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="55" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A55" s="41">
         <v>1993</v>
       </c>
@@ -4443,7 +4443,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="56" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A56" s="39" t="s">
         <v>45</v>
       </c>
